--- a/training.xlsx
+++ b/training.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Training Only\Food-Bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE40C0D1-55ED-45FC-8921-78C442D0BBDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA473B43-0D3F-4E1F-8EB1-C67B093A92E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -19860,10 +19860,10 @@
         <v>23</v>
       </c>
       <c r="G697" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H697" s="2">
-        <v>0</v>
+        <v>5.162037037037037E-3</v>
       </c>
       <c r="I697" s="1">
         <v>46083.763425925928</v>
@@ -20613,10 +20613,10 @@
         <v>27</v>
       </c>
       <c r="G726" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H726" s="2">
-        <v>0</v>
+        <v>7.060185185185185E-3</v>
       </c>
       <c r="I726" s="1">
         <v>46118.752662037034</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Training Only\Food-Bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA473B43-0D3F-4E1F-8EB1-C67B093A92E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5567239-9CC1-4DED-A0D6-5D1CB8DBF0F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3504" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3628" uniqueCount="96">
   <si>
     <t>Company Name</t>
   </si>
@@ -20066,7 +20066,7 @@
         <v>12</v>
       </c>
       <c r="H704" s="2">
-        <v>1.3888888888888889E-4</v>
+        <v>3.0092592592592595E-4</v>
       </c>
       <c r="I704" s="1">
         <v>46083.766203703701</v>
@@ -20338,16 +20338,16 @@
         <v>27</v>
       </c>
       <c r="G715" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H715" s="2">
-        <v>0</v>
+        <v>2.0798611111111111E-2</v>
       </c>
       <c r="I715" s="1">
         <v>46118.771296296298</v>
       </c>
       <c r="J715">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K715" t="s">
         <v>11</v>
@@ -20367,16 +20367,16 @@
         <v>27</v>
       </c>
       <c r="G716" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H716" s="2">
-        <v>0</v>
+        <v>1.2719907407407407E-2</v>
       </c>
       <c r="I716" s="1">
         <v>46118.771296296298</v>
       </c>
       <c r="J716">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K716" t="s">
         <v>11</v>
@@ -20396,16 +20396,16 @@
         <v>27</v>
       </c>
       <c r="G717" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H717" s="2">
-        <v>0</v>
+        <v>7.5462962962962966E-3</v>
       </c>
       <c r="I717" s="1">
         <v>46118.771990740737</v>
       </c>
       <c r="J717">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K717" t="s">
         <v>11</v>
@@ -20461,55 +20461,55 @@
         <v>27</v>
       </c>
       <c r="G720" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H720" s="2">
-        <v>0</v>
+        <v>4.3981481481481481E-4</v>
       </c>
       <c r="I720" s="1">
         <v>46118.772685185184</v>
       </c>
       <c r="J720">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K720" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="721" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B721" t="s">
-        <v>28</v>
-      </c>
-      <c r="C721">
+      <c r="H721" s="2"/>
+      <c r="I721" s="1"/>
+      <c r="K721" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="722" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B722" t="s">
+        <v>28</v>
+      </c>
+      <c r="C722">
         <v>1146</v>
       </c>
-      <c r="D721" t="s">
+      <c r="D722" t="s">
         <v>37</v>
       </c>
-      <c r="F721" t="s">
+      <c r="F722" t="s">
         <v>27</v>
       </c>
-      <c r="G721" t="s">
-        <v>12</v>
-      </c>
-      <c r="H721" s="2">
-        <v>7.9745370370370369E-3</v>
-      </c>
-      <c r="I721" s="1">
+      <c r="G722" t="s">
+        <v>10</v>
+      </c>
+      <c r="H722" s="2">
+        <v>2.9629629629629631E-2</v>
+      </c>
+      <c r="I722" s="1">
         <v>46118.773379629631</v>
       </c>
-      <c r="J721">
+      <c r="J722">
         <v>1</v>
       </c>
-      <c r="K721" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="722" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H722" s="2"/>
-      <c r="I722" s="1"/>
       <c r="K722" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="723" spans="2:11" x14ac:dyDescent="0.25">
@@ -20526,16 +20526,16 @@
         <v>27</v>
       </c>
       <c r="G723" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H723" s="2">
-        <v>0</v>
+        <v>8.9351851851851849E-3</v>
       </c>
       <c r="I723" s="1">
         <v>46118.773379629631</v>
       </c>
       <c r="J723">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K723" t="s">
         <v>11</v>
@@ -20584,10 +20584,10 @@
         <v>27</v>
       </c>
       <c r="G725" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H725" s="2">
-        <v>0</v>
+        <v>7.3958333333333333E-3</v>
       </c>
       <c r="I725" s="1">
         <v>46118.752662037034</v>
@@ -20671,16 +20671,16 @@
         <v>27</v>
       </c>
       <c r="G728" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H728" s="2">
-        <v>0</v>
+        <v>7.3842592592592597E-3</v>
       </c>
       <c r="I728" s="1">
         <v>46118.754050925927</v>
       </c>
       <c r="J728">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K728" t="s">
         <v>11</v>
@@ -20700,10 +20700,10 @@
         <v>27</v>
       </c>
       <c r="G729" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H729" s="2">
-        <v>0</v>
+        <v>1.1909722222222223E-2</v>
       </c>
       <c r="I729" s="1">
         <v>46118.754050925927</v>
@@ -20738,7 +20738,7 @@
         <v>46118.754745370374</v>
       </c>
       <c r="J730">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K730" t="s">
         <v>11</v>
@@ -20816,10 +20816,10 @@
         <v>27</v>
       </c>
       <c r="G733" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H733" s="2">
-        <v>4.3981481481481481E-4</v>
+        <v>8.067129629629629E-3</v>
       </c>
       <c r="I733" s="1">
         <v>46118.755439814813</v>
@@ -20832,10 +20832,32 @@
       </c>
     </row>
     <row r="734" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H734" s="2"/>
-      <c r="I734" s="1"/>
+      <c r="B734" t="s">
+        <v>28</v>
+      </c>
+      <c r="C734">
+        <v>5011</v>
+      </c>
+      <c r="D734" t="s">
+        <v>93</v>
+      </c>
+      <c r="F734" t="s">
+        <v>27</v>
+      </c>
+      <c r="G734" t="s">
+        <v>10</v>
+      </c>
+      <c r="H734" s="2">
+        <v>8.2175925925925923E-3</v>
+      </c>
+      <c r="I734" s="1">
+        <v>46118.75613425926</v>
+      </c>
+      <c r="J734">
+        <v>3</v>
+      </c>
       <c r="K734" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="735" spans="2:11" x14ac:dyDescent="0.25">
@@ -20843,25 +20865,25 @@
         <v>28</v>
       </c>
       <c r="C735">
-        <v>5011</v>
+        <v>1167</v>
       </c>
       <c r="D735" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="F735" t="s">
         <v>27</v>
       </c>
       <c r="G735" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H735" s="2">
-        <v>0</v>
+        <v>6.9097222222222225E-3</v>
       </c>
       <c r="I735" s="1">
-        <v>46118.75613425926</v>
+        <v>46118.756828703707</v>
       </c>
       <c r="J735">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K735" t="s">
         <v>11</v>
@@ -20872,10 +20894,10 @@
         <v>28</v>
       </c>
       <c r="C736">
-        <v>1167</v>
+        <v>5394</v>
       </c>
       <c r="D736" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="F736" t="s">
         <v>27</v>
@@ -20884,7 +20906,7 @@
         <v>10</v>
       </c>
       <c r="H736" s="2">
-        <v>6.9097222222222225E-3</v>
+        <v>1.1458333333333333E-2</v>
       </c>
       <c r="I736" s="1">
         <v>46118.756828703707</v>
@@ -20901,22 +20923,22 @@
         <v>28</v>
       </c>
       <c r="C737">
-        <v>5394</v>
+        <v>2647</v>
       </c>
       <c r="D737" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="F737" t="s">
         <v>27</v>
       </c>
       <c r="G737" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H737" s="2">
-        <v>1.1458333333333333E-2</v>
+        <v>4.0509259259259258E-4</v>
       </c>
       <c r="I737" s="1">
-        <v>46118.756828703707</v>
+        <v>46118.757523148146</v>
       </c>
       <c r="J737">
         <v>0</v>
@@ -20926,39 +20948,39 @@
       </c>
     </row>
     <row r="738" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B738" t="s">
-        <v>28</v>
-      </c>
-      <c r="C738">
-        <v>2647</v>
-      </c>
-      <c r="D738" t="s">
-        <v>72</v>
-      </c>
-      <c r="F738" t="s">
+      <c r="H738" s="2"/>
+      <c r="I738" s="1"/>
+      <c r="K738" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="739" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B739" t="s">
+        <v>28</v>
+      </c>
+      <c r="C739">
+        <v>3865</v>
+      </c>
+      <c r="D739" t="s">
+        <v>88</v>
+      </c>
+      <c r="F739" t="s">
         <v>27</v>
       </c>
-      <c r="G738" t="s">
-        <v>12</v>
-      </c>
-      <c r="H738" s="2">
-        <v>4.0509259259259258E-4</v>
-      </c>
-      <c r="I738" s="1">
-        <v>46118.757523148146</v>
-      </c>
-      <c r="J738">
-        <v>0</v>
-      </c>
-      <c r="K738" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="739" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H739" s="2"/>
-      <c r="I739" s="1"/>
+      <c r="G739" t="s">
+        <v>10</v>
+      </c>
+      <c r="H739" s="2">
+        <v>6.7361111111111111E-3</v>
+      </c>
+      <c r="I739" s="1">
+        <v>46118.758217592593</v>
+      </c>
+      <c r="J739">
+        <v>3</v>
+      </c>
       <c r="K739" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="740" spans="2:11" x14ac:dyDescent="0.25">
@@ -20966,25 +20988,25 @@
         <v>28</v>
       </c>
       <c r="C740">
-        <v>3865</v>
+        <v>1168</v>
       </c>
       <c r="D740" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="F740" t="s">
         <v>27</v>
       </c>
       <c r="G740" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H740" s="2">
-        <v>0</v>
+        <v>7.2569444444444443E-3</v>
       </c>
       <c r="I740" s="1">
         <v>46118.758217592593</v>
       </c>
       <c r="J740">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K740" t="s">
         <v>11</v>
@@ -20995,10 +21017,10 @@
         <v>28</v>
       </c>
       <c r="C741">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="D741" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F741" t="s">
         <v>27</v>
@@ -21007,13 +21029,13 @@
         <v>10</v>
       </c>
       <c r="H741" s="2">
-        <v>7.2569444444444443E-3</v>
+        <v>7.8009259259259256E-3</v>
       </c>
       <c r="I741" s="1">
-        <v>46118.758217592593</v>
+        <v>46118.758912037039</v>
       </c>
       <c r="J741">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K741" t="s">
         <v>11</v>
@@ -21024,10 +21046,10 @@
         <v>28</v>
       </c>
       <c r="C742">
-        <v>1169</v>
+        <v>3270</v>
       </c>
       <c r="D742" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="F742" t="s">
         <v>27</v>
@@ -21036,7 +21058,7 @@
         <v>10</v>
       </c>
       <c r="H742" s="2">
-        <v>7.8009259259259256E-3</v>
+        <v>1.7824074074074075E-3</v>
       </c>
       <c r="I742" s="1">
         <v>46118.758912037039</v>
@@ -21053,126 +21075,727 @@
         <v>28</v>
       </c>
       <c r="C743">
+        <v>1141</v>
+      </c>
+      <c r="D743" t="s">
+        <v>29</v>
+      </c>
+      <c r="F743" t="s">
+        <v>19</v>
+      </c>
+      <c r="G743" t="s">
+        <v>13</v>
+      </c>
+      <c r="H743" s="2">
+        <v>0</v>
+      </c>
+      <c r="I743" s="1">
+        <v>46146.677199074074</v>
+      </c>
+      <c r="J743">
+        <v>0</v>
+      </c>
+      <c r="K743" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="744" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B744" t="s">
+        <v>28</v>
+      </c>
+      <c r="C744">
+        <v>1142</v>
+      </c>
+      <c r="D744" t="s">
+        <v>31</v>
+      </c>
+      <c r="F744" t="s">
+        <v>19</v>
+      </c>
+      <c r="G744" t="s">
+        <v>10</v>
+      </c>
+      <c r="H744" s="2">
+        <v>1.1909722222222223E-2</v>
+      </c>
+      <c r="I744" s="1">
+        <v>46146.677893518521</v>
+      </c>
+      <c r="J744">
+        <v>0</v>
+      </c>
+      <c r="K744" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="745" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B745" t="s">
+        <v>28</v>
+      </c>
+      <c r="C745">
+        <v>1887</v>
+      </c>
+      <c r="D745" t="s">
+        <v>65</v>
+      </c>
+      <c r="F745" t="s">
+        <v>19</v>
+      </c>
+      <c r="G745" t="s">
+        <v>13</v>
+      </c>
+      <c r="H745" s="2">
+        <v>0</v>
+      </c>
+      <c r="I745" s="1">
+        <v>46146.677893518521</v>
+      </c>
+      <c r="J745">
+        <v>0</v>
+      </c>
+      <c r="K745" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="746" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B746" t="s">
+        <v>28</v>
+      </c>
+      <c r="C746">
+        <v>4979</v>
+      </c>
+      <c r="D746" t="s">
+        <v>92</v>
+      </c>
+      <c r="F746" t="s">
+        <v>19</v>
+      </c>
+      <c r="G746" t="s">
+        <v>10</v>
+      </c>
+      <c r="H746" s="2">
+        <v>5.5324074074074078E-3</v>
+      </c>
+      <c r="I746" s="1">
+        <v>46146.678587962961</v>
+      </c>
+      <c r="J746">
+        <v>0</v>
+      </c>
+      <c r="K746" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="747" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B747" t="s">
+        <v>28</v>
+      </c>
+      <c r="C747">
+        <v>1144</v>
+      </c>
+      <c r="D747" t="s">
+        <v>32</v>
+      </c>
+      <c r="F747" t="s">
+        <v>19</v>
+      </c>
+      <c r="G747" t="s">
+        <v>13</v>
+      </c>
+      <c r="H747" s="2">
+        <v>0</v>
+      </c>
+      <c r="I747" s="1">
+        <v>46146.679282407407</v>
+      </c>
+      <c r="J747">
+        <v>0</v>
+      </c>
+      <c r="K747" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="748" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B748" t="s">
+        <v>28</v>
+      </c>
+      <c r="C748">
+        <v>1146</v>
+      </c>
+      <c r="D748" t="s">
+        <v>37</v>
+      </c>
+      <c r="F748" t="s">
+        <v>19</v>
+      </c>
+      <c r="G748" t="s">
+        <v>10</v>
+      </c>
+      <c r="H748" s="2">
+        <v>8.9236111111111113E-3</v>
+      </c>
+      <c r="I748" s="1">
+        <v>46146.679976851854</v>
+      </c>
+      <c r="J748">
+        <v>0</v>
+      </c>
+      <c r="K748" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="749" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B749" t="s">
+        <v>28</v>
+      </c>
+      <c r="C749">
+        <v>1152</v>
+      </c>
+      <c r="D749" t="s">
+        <v>41</v>
+      </c>
+      <c r="F749" t="s">
+        <v>19</v>
+      </c>
+      <c r="G749" t="s">
+        <v>13</v>
+      </c>
+      <c r="H749" s="2">
+        <v>0</v>
+      </c>
+      <c r="I749" s="1">
+        <v>46146.679976851854</v>
+      </c>
+      <c r="J749">
+        <v>0</v>
+      </c>
+      <c r="K749" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="750" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B750" t="s">
+        <v>28</v>
+      </c>
+      <c r="C750">
+        <v>1159</v>
+      </c>
+      <c r="D750" t="s">
+        <v>42</v>
+      </c>
+      <c r="F750" t="s">
+        <v>19</v>
+      </c>
+      <c r="G750" t="s">
+        <v>13</v>
+      </c>
+      <c r="H750" s="2">
+        <v>0</v>
+      </c>
+      <c r="I750" s="1">
+        <v>46146.680671296293</v>
+      </c>
+      <c r="J750">
+        <v>0</v>
+      </c>
+      <c r="K750" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="751" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B751" t="s">
+        <v>28</v>
+      </c>
+      <c r="C751">
+        <v>1153</v>
+      </c>
+      <c r="D751" t="s">
+        <v>44</v>
+      </c>
+      <c r="F751" t="s">
+        <v>19</v>
+      </c>
+      <c r="G751" t="s">
+        <v>10</v>
+      </c>
+      <c r="H751" s="2">
+        <v>5.5208333333333333E-3</v>
+      </c>
+      <c r="I751" s="1">
+        <v>46146.68136574074</v>
+      </c>
+      <c r="J751">
+        <v>0</v>
+      </c>
+      <c r="K751" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="752" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B752" t="s">
+        <v>28</v>
+      </c>
+      <c r="C752">
+        <v>1157</v>
+      </c>
+      <c r="D752" t="s">
+        <v>45</v>
+      </c>
+      <c r="F752" t="s">
+        <v>19</v>
+      </c>
+      <c r="G752" t="s">
+        <v>13</v>
+      </c>
+      <c r="H752" s="2">
+        <v>0</v>
+      </c>
+      <c r="I752" s="1">
+        <v>46146.68136574074</v>
+      </c>
+      <c r="J752">
+        <v>0</v>
+      </c>
+      <c r="K752" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="753" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B753" t="s">
+        <v>28</v>
+      </c>
+      <c r="C753">
+        <v>1158</v>
+      </c>
+      <c r="D753" t="s">
+        <v>46</v>
+      </c>
+      <c r="F753" t="s">
+        <v>19</v>
+      </c>
+      <c r="G753" t="s">
+        <v>10</v>
+      </c>
+      <c r="H753" s="2">
+        <v>7.083333333333333E-3</v>
+      </c>
+      <c r="I753" s="1">
+        <v>46146.682060185187</v>
+      </c>
+      <c r="J753">
+        <v>0</v>
+      </c>
+      <c r="K753" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="754" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B754" t="s">
+        <v>28</v>
+      </c>
+      <c r="C754">
+        <v>4945</v>
+      </c>
+      <c r="D754" t="s">
+        <v>90</v>
+      </c>
+      <c r="F754" t="s">
+        <v>19</v>
+      </c>
+      <c r="G754" t="s">
+        <v>10</v>
+      </c>
+      <c r="H754" s="2">
+        <v>4.7800925925925927E-3</v>
+      </c>
+      <c r="I754" s="1">
+        <v>46146.682754629626</v>
+      </c>
+      <c r="J754">
+        <v>0</v>
+      </c>
+      <c r="K754" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="755" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B755" t="s">
+        <v>28</v>
+      </c>
+      <c r="C755">
+        <v>1162</v>
+      </c>
+      <c r="D755" t="s">
+        <v>50</v>
+      </c>
+      <c r="F755" t="s">
+        <v>19</v>
+      </c>
+      <c r="G755" t="s">
+        <v>13</v>
+      </c>
+      <c r="H755" s="2">
+        <v>0</v>
+      </c>
+      <c r="I755" s="1">
+        <v>46146.682754629626</v>
+      </c>
+      <c r="J755">
+        <v>0</v>
+      </c>
+      <c r="K755" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="756" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B756" t="s">
+        <v>28</v>
+      </c>
+      <c r="C756">
+        <v>1163</v>
+      </c>
+      <c r="D756" t="s">
+        <v>51</v>
+      </c>
+      <c r="F756" t="s">
+        <v>19</v>
+      </c>
+      <c r="G756" t="s">
+        <v>13</v>
+      </c>
+      <c r="H756" s="2">
+        <v>0</v>
+      </c>
+      <c r="I756" s="1">
+        <v>46146.683449074073</v>
+      </c>
+      <c r="J756">
+        <v>0</v>
+      </c>
+      <c r="K756" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="757" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B757" t="s">
+        <v>28</v>
+      </c>
+      <c r="C757">
+        <v>1882</v>
+      </c>
+      <c r="D757" t="s">
+        <v>67</v>
+      </c>
+      <c r="F757" t="s">
+        <v>19</v>
+      </c>
+      <c r="G757" t="s">
+        <v>10</v>
+      </c>
+      <c r="H757" s="2">
+        <v>4.5138888888888885E-3</v>
+      </c>
+      <c r="I757" s="1">
+        <v>46146.68414351852</v>
+      </c>
+      <c r="J757">
+        <v>0</v>
+      </c>
+      <c r="K757" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="758" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B758" t="s">
+        <v>28</v>
+      </c>
+      <c r="C758">
+        <v>4634</v>
+      </c>
+      <c r="D758" t="s">
+        <v>89</v>
+      </c>
+      <c r="F758" t="s">
+        <v>19</v>
+      </c>
+      <c r="G758" t="s">
+        <v>10</v>
+      </c>
+      <c r="H758" s="2">
+        <v>4.5486111111111109E-3</v>
+      </c>
+      <c r="I758" s="1">
+        <v>46146.68414351852</v>
+      </c>
+      <c r="J758">
+        <v>0</v>
+      </c>
+      <c r="K758" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="759" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B759" t="s">
+        <v>28</v>
+      </c>
+      <c r="C759">
+        <v>1166</v>
+      </c>
+      <c r="D759" t="s">
+        <v>53</v>
+      </c>
+      <c r="F759" t="s">
+        <v>19</v>
+      </c>
+      <c r="G759" t="s">
+        <v>13</v>
+      </c>
+      <c r="H759" s="2">
+        <v>0</v>
+      </c>
+      <c r="I759" s="1">
+        <v>46146.684837962966</v>
+      </c>
+      <c r="J759">
+        <v>0</v>
+      </c>
+      <c r="K759" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="760" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B760" t="s">
+        <v>28</v>
+      </c>
+      <c r="C760">
+        <v>5011</v>
+      </c>
+      <c r="D760" t="s">
+        <v>93</v>
+      </c>
+      <c r="F760" t="s">
+        <v>19</v>
+      </c>
+      <c r="G760" t="s">
+        <v>13</v>
+      </c>
+      <c r="H760" s="2">
+        <v>0</v>
+      </c>
+      <c r="I760" s="1">
+        <v>46146.685532407406</v>
+      </c>
+      <c r="J760">
+        <v>0</v>
+      </c>
+      <c r="K760" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="761" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B761" t="s">
+        <v>28</v>
+      </c>
+      <c r="C761">
+        <v>1167</v>
+      </c>
+      <c r="D761" t="s">
+        <v>55</v>
+      </c>
+      <c r="F761" t="s">
+        <v>19</v>
+      </c>
+      <c r="G761" t="s">
+        <v>13</v>
+      </c>
+      <c r="H761" s="2">
+        <v>0</v>
+      </c>
+      <c r="I761" s="1">
+        <v>46146.686226851853</v>
+      </c>
+      <c r="J761">
+        <v>0</v>
+      </c>
+      <c r="K761" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="762" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B762" t="s">
+        <v>28</v>
+      </c>
+      <c r="C762">
+        <v>5394</v>
+      </c>
+      <c r="D762" t="s">
+        <v>95</v>
+      </c>
+      <c r="F762" t="s">
+        <v>19</v>
+      </c>
+      <c r="G762" t="s">
+        <v>13</v>
+      </c>
+      <c r="H762" s="2">
+        <v>0</v>
+      </c>
+      <c r="I762" s="1">
+        <v>46146.686226851853</v>
+      </c>
+      <c r="J762">
+        <v>0</v>
+      </c>
+      <c r="K762" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="763" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B763" t="s">
+        <v>28</v>
+      </c>
+      <c r="C763">
+        <v>2647</v>
+      </c>
+      <c r="D763" t="s">
+        <v>72</v>
+      </c>
+      <c r="F763" t="s">
+        <v>19</v>
+      </c>
+      <c r="G763" t="s">
+        <v>10</v>
+      </c>
+      <c r="H763" s="2">
+        <v>7.951388888888888E-3</v>
+      </c>
+      <c r="I763" s="1">
+        <v>46146.686921296299</v>
+      </c>
+      <c r="J763">
+        <v>0</v>
+      </c>
+      <c r="K763" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="764" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B764" t="s">
+        <v>28</v>
+      </c>
+      <c r="C764">
+        <v>3865</v>
+      </c>
+      <c r="D764" t="s">
+        <v>88</v>
+      </c>
+      <c r="F764" t="s">
+        <v>19</v>
+      </c>
+      <c r="G764" t="s">
+        <v>10</v>
+      </c>
+      <c r="H764" s="2">
+        <v>4.363425925925926E-3</v>
+      </c>
+      <c r="I764" s="1">
+        <v>46146.687615740739</v>
+      </c>
+      <c r="J764">
+        <v>0</v>
+      </c>
+      <c r="K764" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="765" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B765" t="s">
+        <v>28</v>
+      </c>
+      <c r="C765">
+        <v>1168</v>
+      </c>
+      <c r="D765" t="s">
+        <v>57</v>
+      </c>
+      <c r="F765" t="s">
+        <v>19</v>
+      </c>
+      <c r="G765" t="s">
+        <v>10</v>
+      </c>
+      <c r="H765" s="2">
+        <v>6.2384259259259259E-3</v>
+      </c>
+      <c r="I765" s="1">
+        <v>46146.687615740739</v>
+      </c>
+      <c r="J765">
+        <v>0</v>
+      </c>
+      <c r="K765" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="766" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B766" t="s">
+        <v>28</v>
+      </c>
+      <c r="C766">
+        <v>1169</v>
+      </c>
+      <c r="D766" t="s">
+        <v>58</v>
+      </c>
+      <c r="F766" t="s">
+        <v>19</v>
+      </c>
+      <c r="G766" t="s">
+        <v>10</v>
+      </c>
+      <c r="H766" s="2">
+        <v>4.9421296296296297E-3</v>
+      </c>
+      <c r="I766" s="1">
+        <v>46146.688310185185</v>
+      </c>
+      <c r="J766">
+        <v>0</v>
+      </c>
+      <c r="K766" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="767" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B767" t="s">
+        <v>28</v>
+      </c>
+      <c r="C767">
         <v>3270</v>
       </c>
-      <c r="D743" t="s">
+      <c r="D767" t="s">
         <v>85</v>
       </c>
-      <c r="F743" t="s">
-        <v>27</v>
-      </c>
-      <c r="G743" t="s">
-        <v>10</v>
-      </c>
-      <c r="H743" s="2">
-        <v>1.7824074074074075E-3</v>
-      </c>
-      <c r="I743" s="1">
-        <v>46118.758912037039</v>
-      </c>
-      <c r="J743">
-        <v>0</v>
-      </c>
-      <c r="K743" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="744" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H744" s="2"/>
-      <c r="I744" s="1"/>
-    </row>
-    <row r="745" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H745" s="2"/>
-      <c r="I745" s="1"/>
-    </row>
-    <row r="746" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="I746" s="1"/>
-    </row>
-    <row r="747" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H747" s="2"/>
-      <c r="I747" s="1"/>
-    </row>
-    <row r="748" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H748" s="2"/>
-      <c r="I748" s="1"/>
-    </row>
-    <row r="749" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H749" s="2"/>
-      <c r="I749" s="1"/>
-    </row>
-    <row r="750" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H750" s="2"/>
-      <c r="I750" s="1"/>
-    </row>
-    <row r="751" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H751" s="2"/>
-      <c r="I751" s="1"/>
-    </row>
-    <row r="752" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H752" s="2"/>
-      <c r="I752" s="1"/>
-    </row>
-    <row r="753" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H753" s="2"/>
-      <c r="I753" s="1"/>
-    </row>
-    <row r="754" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H754" s="2"/>
-      <c r="I754" s="1"/>
-    </row>
-    <row r="755" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H755" s="2"/>
-      <c r="I755" s="1"/>
-    </row>
-    <row r="756" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H756" s="2"/>
-      <c r="I756" s="1"/>
-    </row>
-    <row r="757" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H757" s="2"/>
-      <c r="I757" s="1"/>
-    </row>
-    <row r="758" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H758" s="2"/>
-      <c r="I758" s="1"/>
-    </row>
-    <row r="759" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H759" s="2"/>
-      <c r="I759" s="1"/>
-    </row>
-    <row r="760" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H760" s="2"/>
-      <c r="I760" s="1"/>
-    </row>
-    <row r="761" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H761" s="2"/>
-      <c r="I761" s="1"/>
-    </row>
-    <row r="762" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H762" s="2"/>
-      <c r="I762" s="1"/>
-    </row>
-    <row r="763" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H763" s="2"/>
-      <c r="I763" s="1"/>
-    </row>
-    <row r="764" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H764" s="2"/>
-      <c r="I764" s="1"/>
-    </row>
-    <row r="765" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H765" s="2"/>
-      <c r="I765" s="1"/>
-    </row>
-    <row r="766" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H766" s="2"/>
-      <c r="I766" s="1"/>
-    </row>
-    <row r="767" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H767" s="2"/>
-      <c r="I767" s="1"/>
-    </row>
-    <row r="768" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="F767" t="s">
+        <v>19</v>
+      </c>
+      <c r="G767" t="s">
+        <v>10</v>
+      </c>
+      <c r="H767" s="2">
+        <v>4.7685185185185183E-3</v>
+      </c>
+      <c r="I767" s="1">
+        <v>46146.689004629632</v>
+      </c>
+      <c r="J767">
+        <v>0</v>
+      </c>
+      <c r="K767" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="768" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H768" s="2"/>
       <c r="I768" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Training Only\Food-Bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BD391F-5AC1-443A-9C4B-9AA2D6054B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE0E329-5A18-4C99-A4C4-76BAFE9C1A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{EDE2166C-0BB1-4E42-9CFB-15DE41BF2782}"/>
   </bookViews>
@@ -709,42 +709,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5B20F41-EE91-4DA9-A42F-74B252A0555C}">
-  <dimension ref="A1:K6671"/>
+  <dimension ref="B1:K6671"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>34</v>
       </c>
@@ -773,7 +773,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>34</v>
       </c>
@@ -802,7 +802,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>34</v>
       </c>
@@ -831,7 +831,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>34</v>
       </c>
@@ -860,7 +860,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>34</v>
       </c>
@@ -889,14 +889,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H7" s="2"/>
       <c r="I7" s="1"/>
       <c r="K7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>34</v>
       </c>
@@ -925,7 +925,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>34</v>
       </c>
@@ -954,7 +954,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>34</v>
       </c>
@@ -983,7 +983,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>34</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>34</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>34</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>34</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>34</v>
       </c>
@@ -1128,7 +1128,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>34</v>
       </c>
